--- a/public/excel/product/Gia thép I.xlsx
+++ b/public/excel/product/Gia thép I.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép hình I 100 x 55 x 4.5 x 6m</t>
   </si>
   <si>
@@ -57,6 +60,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép hình I 120 x 64 x 4.8 x 6m</t>
@@ -515,7 +521,9 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -575,7 +583,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>6</v>
@@ -596,12 +604,14 @@
         <v>908.772</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -661,7 +671,7 @@
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>6</v>
@@ -673,21 +683,23 @@
         <v>14.545</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>16</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -747,7 +759,7 @@
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>12</v>
@@ -759,21 +771,23 @@
         <v>14.545</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -833,7 +847,7 @@
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>12</v>
@@ -845,21 +859,23 @@
         <v>17.818</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>19.6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -919,7 +935,7 @@
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>12</v>
@@ -931,21 +947,23 @@
         <v>17.273</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>19</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1005,7 +1023,7 @@
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>12</v>
@@ -1017,21 +1035,23 @@
         <v>17.273</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>19</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1091,7 +1111,7 @@
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>12</v>
@@ -1103,21 +1123,23 @@
         <v>18.818</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1177,7 +1199,7 @@
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>12</v>
@@ -1189,21 +1211,23 @@
         <v>18.818</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1263,7 +1287,7 @@
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>12</v>
@@ -1275,21 +1299,23 @@
         <v>18.818</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -1349,7 +1375,7 @@
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>12</v>
@@ -1361,21 +1387,23 @@
         <v>18.818</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -1435,7 +1463,7 @@
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>12</v>
@@ -1447,21 +1475,23 @@
         <v>18.818</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1521,7 +1551,7 @@
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>12</v>
@@ -1533,21 +1563,23 @@
         <v>18.818</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -1607,7 +1639,7 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>12</v>
@@ -1619,21 +1651,23 @@
         <v>18.818</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>20.7</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J14" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1693,7 +1727,7 @@
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>12</v>
@@ -1705,21 +1739,23 @@
         <v>18.318</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1779,7 +1815,7 @@
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>12</v>
@@ -1791,21 +1827,23 @@
         <v>18.318</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1865,7 +1903,7 @@
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>12</v>
@@ -1877,21 +1915,23 @@
         <v>18.318</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J17" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -1951,7 +1991,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>12</v>
@@ -1963,21 +2003,23 @@
         <v>18.318</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J18" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2037,7 +2079,7 @@
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>12</v>
@@ -2049,21 +2091,23 @@
         <v>18.318</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J19" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2123,7 +2167,7 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>12</v>
@@ -2135,21 +2179,23 @@
         <v>18.318</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J20" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2209,7 +2255,7 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>12</v>
@@ -2221,21 +2267,23 @@
         <v>18.318</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2295,7 +2343,7 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>12</v>
@@ -2307,21 +2355,23 @@
         <v>18.318</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J22" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -2381,7 +2431,7 @@
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>12</v>
@@ -2393,21 +2443,23 @@
         <v>18.318</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -2467,7 +2519,7 @@
     </row>
     <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>12</v>
@@ -2479,21 +2531,23 @@
         <v>18.318</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>20.15</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J24" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
